--- a/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_lowerbound/comparison_results_lowerbound.xlsx
+++ b/SLPSO/DRLPSO_CEC2021_先前的数据/Analyze_of_bound/changing_lowerbound/comparison_results_lowerbound.xlsx
@@ -478,27 +478,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.92E-221±0.00E+00 (≈)</t>
+          <t>3.92E-221±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.82E-222±0.00E+00 (≈)</t>
+          <t>2.82E-222±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.80E-219±0.00E+00 (≈)</t>
+          <t>1.80E-219±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.23E-220±0.00E+00 (≈)</t>
+          <t>2.23E-220±0.00E+00 (-)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.32E-222±0.00E+00 (≈)</t>
+          <t>2.32E-222±0.00E+00 (-)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.05E+02±8.24E+01 (≈)</t>
+          <t>1.05E+02±8.24E+01 (-)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.90E+00±4.02E+00 (≈)</t>
+          <t>9.90E+00±4.02E+00 (-)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.01E+01±3.97E+00 (≈)</t>
+          <t>1.01E+01±3.97E+00 (-)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.66E+01±9.03E+01 (≈)</t>
+          <t>7.66E+01±9.03E+01 (+)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -663,27 +663,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.37E+01±3.58E+01 (≈)</t>
+          <t>1.37E+01±3.58E+01 (-)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19E+01±3.24E+01 (≈)</t>
+          <t>1.19E+01±3.24E+01 (-)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.01E+01±3.28E+01 (≈)</t>
+          <t>1.01E+01±3.28E+01 (-)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.58E+00±4.51E+00 (≈)</t>
+          <t>2.58E+00±4.51E+00 (-)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.12E+01±2.99E+01 (≈)</t>
+          <t>1.12E+01±2.99E+01 (-)</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.67E+01±5.43E+01 (≈)</t>
+          <t>2.67E+01±5.43E+01 (+)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.37E+01±7.27E+01 (≈)</t>
+          <t>5.37E+01±7.27E+01 (+)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.47E+01±6.43E+01 (≈)</t>
+          <t>4.47E+01±6.43E+01 (+)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.76E+01±7.25E+01 (≈)</t>
+          <t>4.76E+01±7.25E+01 (+)</t>
         </is>
       </c>
     </row>
@@ -737,27 +737,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30E-01±1.81E+00 (≈)</t>
+          <t>3.30E-01±1.81E+00 (-)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.30E-01±1.81E+00 (≈)</t>
+          <t>3.30E-01±1.81E+00 (-)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.03E-01±2.21E+00 (≈)</t>
+          <t>4.03E-01±2.21E+00 (-)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.69E-01±2.02E+00 (≈)</t>
+          <t>3.69E-01±2.02E+00 (-)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.77E-01±2.58E+00 (≈)</t>
+          <t>6.77E-01±2.58E+00 (-)</t>
         </is>
       </c>
     </row>
@@ -774,27 +774,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.88E-15±1.60E-30 (≈)</t>
+          <t>8.88E-15±1.60E-30 (-)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.88E-15±1.60E-30 (≈)</t>
+          <t>8.88E-15±1.60E-30 (-)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.88E-15±1.60E-30 (≈)</t>
+          <t>8.88E-15±1.60E-30 (-)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.88E-15±1.60E-30 (≈)</t>
+          <t>8.88E-15±1.60E-30 (-)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.88E-15±1.60E-30 (≈)</t>
+          <t>8.88E-15±1.60E-30 (-)</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.91E+01±5.44E+00 (≈)</t>
+          <t>4.91E+01±5.44E+00 (+)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -844,27 +844,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/4/5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/5/4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>2/4/4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/5/4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0/10/0</t>
+          <t>1/3/6</t>
         </is>
       </c>
     </row>
